--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -811,7 +811,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2623,6 +2623,28 @@
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>noetic_bevy split by feature: components.rs removed, systems.rs renamed think.rs (MOD-028 noetic_bevy::think). NoeticAgent and AgentBrainState live in think, world markers in sync, NavAgent in nav. Modules diagram updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="29" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>noetic_bevy and noetic_runtime merged into one crate, noetic, the crate games add; it re-exports noetic_core. Workspace, modules, dependency rules and matrix, types, ECS and modules diagram updated.</t>
         </is>
       </c>
     </row>
@@ -3028,9 +3050,8 @@
 │  │  └─ src/{lib.rs, model/, agent/, world/, sim.rs, perception.rs, emotion.rs, reaction.rs,
 │  │          utility.rs, steps.rs, social.rs, conflict.rs, territory.rs, locomotion.rs,
 │  │          personality.rs, rng.rs, io/, ext.rs, sandbox.rs, tuning.rs, events.rs}
-│  ├─ noetic_bevy/            # Bevy plugin
+│  ├─ noetic/                 # the crate games add: Bevy plugin, pub use noetic_core, prelude
 │  │  └─ src/{lib.rs, plugin.rs, asset.rs, sync.rs, think.rs, anim.rs, nav.rs, debug.rs}
-│  ├─ noetic_runtime/         # facade: pub use noetic_core + noetic_bevy, prelude
 │  └─ noetic_editor/          # binary
 │     └─ src/{main.rs, app.rs, theme.rs, i18n.rs, shell/, project/, brain/, world/,
 │             inspector.rs, species/, individuals/, io/, remote.rs}
@@ -3099,7 +3120,7 @@
     <row r="10" ht="29" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -3120,140 +3141,116 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="29" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>noetic_runtime</t>
+          <t>noetic_editor</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>lib</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>noetic_core, noetic_bevy</t>
+          <t>bevy (ui, feathers, winit, render), noetic[debug], arboard, rfd, ureq (BRP client)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>debug (forwards)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
     </row>
-    <row r="12" ht="29" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>bin</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>bevy (ui, feathers, winit, render), noetic_runtime[debug], arboard, rfd, ureq (BRP client)</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>2.3 Build profiles</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Profile</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Use</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="29" customHeight="1">
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="29" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>opt-level 1; dependencies opt-level 3</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Daily development (Bevy recommendation)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>dev</t>
+          <t>release</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>opt-level 1; dependencies opt-level 3</t>
+          <t>lto = "thin", codegen-units = 1</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Daily development (Bevy recommendation)</t>
+          <t>Editor binaries; games</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" ht="29" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>ci</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>lto = "thin", codegen-units = 1</t>
+          <t>inherits dev; debug-assertions on</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Editor binaries; games</t>
+          <t>Tests and determinism checks</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="29" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>ci</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>inherits dev; debug-assertions on</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Tests and determinism checks</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3998,12 +3995,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::anim</t>
+          <t>noetic::anim</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -4028,12 +4025,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::asset</t>
+          <t>noetic::asset</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -4058,12 +4055,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::debug</t>
+          <t>noetic::debug</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -4088,12 +4085,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::nav</t>
+          <t>noetic::nav</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -4118,17 +4115,17 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::plugin</t>
+          <t>noetic::plugin</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>NoeticPlugin.</t>
+          <t>NoeticPlugin; prelude, pub use noetic_core.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -4148,12 +4145,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::sync</t>
+          <t>noetic::sync</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -4178,12 +4175,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy::think</t>
+          <t>noetic::think</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5207,7 +5204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5280,7 +5277,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy depends on noetic_core only (plus bevy).</t>
+          <t>noetic depends on noetic_core only (plus bevy) and re-exports it.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -5297,12 +5294,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Games depend on noetic_runtime only.</t>
+          <t>Games depend on noetic only.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>One stable entry point.</t>
+          <t>One entry point: noetic re-exports noetic_core.</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5311,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor uses noetic_runtime, never internal paths of core/bevy.</t>
+          <t>noetic_editor depends on noetic only, never on internal paths.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5394,25 +5391,20 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>noetic_runtime</t>
+          <t>noetic_editor</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>noetic_editor</t>
+          <t>bevy</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>bevy</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>bevy_feathers</t>
         </is>
@@ -5433,12 +5425,11 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>noetic_bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -5452,75 +5443,40 @@
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>noetic_runtime</t>
+          <t>noetic_editor</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>(via noetic)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>noetic_editor</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>(via runtime)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>(via runtime)</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -6036,7 +5992,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Implemented by SimWorld and by noetic_bevy::sync::WorldViewCache</t>
+          <t>Implemented by SimWorld and by noetic::sync::WorldViewCache</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6293,7 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>6.1 Components (runtime, noetic_bevy)</t>
+          <t>6.1 Components (runtime, noetic)</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6729,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -6800,7 +6756,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -6827,7 +6783,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>core/bevy</t>
+          <t>core/noetic</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -7111,7 +7067,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -7138,7 +7094,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -7165,7 +7121,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -7441,7 +7397,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -7468,7 +7424,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -7495,7 +7451,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -7522,7 +7478,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>bevy</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -256,7 +256,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9515475" cy="4352925"/>
+    <ext cx="9515475" cy="4138746"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -773,11 +773,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>内部設計書</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -799,7 +795,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Internal Design (内部設計書)</t>
+          <t>Internal Design</t>
         </is>
       </c>
     </row>
@@ -811,7 +807,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -871,7 +867,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Requirements Definition · Basic Design (基本設計書) · External Design (外部設計書) · Detailed Design (詳細設計書: API specs and algorithms)</t>
+          <t>Requirements Definition · Basic Design · External Design · Detailed Design (API specs and algorithms)</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2645,6 +2641,28 @@
       <c r="D6" s="4" t="inlineStr">
         <is>
           <t>noetic_bevy and noetic_runtime merged into one crate, noetic, the crate games add; it re-exports noetic_core. Workspace, modules, dependency rules and matrix, types, ECS and modules diagram updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Japanese names removed; the documents are in English only.</t>
         </is>
       </c>
     </row>

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>fear &gt; threshold</t>
+          <t>fear &gt; threshold, or challenged and not fighting back (Flee)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="52" ht="29" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>InActivity</t>
+          <t>Choosing / InActivity</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>urge to fight ≥ 70 &amp; rival ≤ 12 m</t>
+          <t>urge to fight ≥ 70 &amp; rival ≤ 12 m, or challenged (Effect::Challenge) and fighting back</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>approach rival</t>
+          <t>approach rival / answer the challenge</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>API-COR-013</t>
+          <t>API-COR-013, API-COR-022</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1292,7 +1292,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>SEQ-01 Game frame with NoeticPlugin (PRC-01…16)</t>
+          <t>SEQ-01 Game frame with NoeticPlugin (PRC-01…17)</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="29" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>PF-01</t>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Decisions at think_hz (default 10 Hz) spread round-robin over frames; movement every fixed step (60 Hz).</t>
+          <t>Decisions at think_hz (default 10 Hz): each agent thinks on the fixed steps where think_due (API-COR-023) is true, so 1/stride of the agents think per step; movement intent every fixed step (60 Hz).</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="55" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>PF-04</t>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Think stage can run agents in parallel (par_iter_mut) because each agent writes only itself; cross-agent effects (alarms, damage) are queued as events and applied in a serial stage. Determinism kept by applying queued effects sorted by agent id.</t>
+          <t>Think can run agents in parallel (par_iter_mut): each agent writes only itself and its own Effect buffer. Effects (alarms, damage, challenges, marks) are applied in NoeticSet::Apply, sorted by (source id, seq), so results do not depend on threads or query order.</t>
         </is>
       </c>
     </row>
@@ -2092,6 +2092,40 @@
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t>f32 only, no fast-math; same operation order; tests compare bit-exact on the same platform and with tolerance across platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="68" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PF-08</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Time steps</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Act and Apply get dt = fixed_dt (1/60 s). Think gets THINK_DT = stride × fixed_dt with stride = max(1, round(fixed_hz / think_hz)) (60 / 10 → 6 → 0.1 s), the same for every agent and every think, whatever the frame rate. Rates per game hour use dt_h = dt / secs_per_game_hour. Editor speed (½×–16×) changes how many fixed steps run per frame, never dt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PF-09</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Agent order</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Bevy queries have no stable order. sync_world_system gives each new agent an AgentId from a counter (new agents of the same step sorted by Entity); AgentOrder keeps (AgentId, Entity) sorted, and Think, Act and Apply walk it. The editor SimWorld keeps its agents in id order.</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2663,6 +2697,72 @@
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Japanese names removed; the documents are in English only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>The game moves the animals: CMP-06 NavAgent replaced by MoveIntent / MoveFailed; MOD-009, MOD-025, MOD-027, SYS-04 and PF-01 updated. Sync reads agent positions back and answers terrain from marker zones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>One agent pipeline for the editor and the game (MOD-015 noetic_core::sim: think_agent, act_agent, think_due, Effect). New TYP-23 Effect, CMP-07 ScentMark, RES-13 AgentOrder, RES-14 NoeticClock, SYS-11 NoeticSet::Apply; PF-08 time steps and PF-09 agent order; PF-01, PF-04, RES-01, SYS-03, SYS-04, MOD-027, MOD-028 updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Coherence review: new TYP-24 Outbox carries an agent's effects and SimEvents; WorldView gets hour() and marks_near(); CMP-02 holds the Outbox; a challenged agent fights back or flees (7.1); MOD-062…064 for model, events and tuning; MOD-015 and MOD-028 API counts; SEQ-01 covers PRC-17.</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2855,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Module diagram and 61 modules with their APIs</t>
+          <t>Module diagram and 64 modules with their APIs</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2885,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Class diagram and 22 main types</t>
+          <t>Class diagram and 24 main types</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3615,7 +3715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
+    <row r="38" ht="29" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>MOD-009</t>
@@ -3633,7 +3733,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Gaits, terrain speed.</t>
+          <t>Gaits and movement intent (Movement); simple mover with terrain speed for SimWorld (editor only).</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3795,7 +3895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
+    <row r="44" ht="42" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>MOD-015</t>
@@ -3813,16 +3913,16 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>tick pipeline (PRC order).</t>
+          <t>One agent pipeline shared by the editor and the game: think_agent, act_agent, think_due, Effect and apply_effect; tick drives a SimWorld (editor).</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>API-COR-001</t>
+          <t>API-COR-001, API-COR-020…023</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
@@ -4095,7 +4195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
+    <row r="54" ht="29" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>MOD-025</t>
@@ -4113,7 +4213,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Navigation adapter; NavAgent.</t>
+          <t>Movement intent out (MoveIntent), MoveFailed back; the game moves the body.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -4155,7 +4255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
+    <row r="56" ht="42" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
           <t>MOD-027</t>
@@ -4173,7 +4273,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Game components → world view; world markers (WaterSource, Burrow…).</t>
+          <t>Game components → world view; world markers and zones (WaterSource, Burrow, Cover, Mud…); agent positions read back; AgentId for new agents, AgentOrder.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4185,7 +4285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1">
+    <row r="57" ht="29" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>MOD-028</t>
@@ -4203,16 +4303,16 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Think/act systems; NoeticAgent, AgentBrainState.</t>
+          <t>Think, act and apply systems; NoeticAgent, AgentBrainState, AgentOrder.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>API-RT-005</t>
+          <t>API-RT-005, API-RT-010, API-RT-011</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" ht="29" customHeight="1">
@@ -5203,6 +5303,96 @@
       </c>
       <c r="F90" s="4" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="91" ht="29" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>MOD-062</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::model</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Species, Brain, Activity, Step and their enums (TYP-01…10); types only.</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>MOD-063</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::events</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>SimEvent (TYP-16); types only.</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" ht="29" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>MOD-064</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::tuning</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Initial tuning constants of the ALG-xx formulas, in one place.</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5516,7 +5706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5877,7 +6067,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>See Detailed Design › Data Detail</t>
+          <t>Variants in Basic Design › 6 Data Design and Detailed Design › Data Detail</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -5982,7 +6172,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="42" customHeight="1">
+    <row r="31" ht="55" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>TYP-14</t>
@@ -6005,12 +6195,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>fn nearest(kind, pos, r) / fn neighbours(pos, r) / fn terrain_at(pos) / fn light() / fn wind()</t>
+          <t>fn nearest(kind, pos, r) / fn neighbours(pos, r) / fn terrain_at(pos) / fn light() / fn wind() / fn hour() / fn marks_near(pos, r)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Implemented by SimWorld and by noetic::sync::WorldViewCache</t>
+          <t>Read-only. Implemented by SimWorld and by noetic::sync::WorldViewCache; per-agent core functions get &amp;dyn WorldView, never the world itself</t>
         </is>
       </c>
     </row>
@@ -6259,6 +6449,70 @@
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>See 9 Errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TYP-23</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>struct</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::sim</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>source: AgentId, seq: u16, kind: Alarm{kind, pos} | Damage{target, dmg} | Challenge{target} | Mark{pos, kind, meaning}</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>What one agent does to others; queued, applied in (source, seq) order (PF-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TYP-24</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Outbox</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>struct</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>noetic_core::sim</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>effects: Vec&lt;Effect&gt;, events: SmallVec&lt;[SimEvent; 8]&gt;, next seq</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>One per agent; think_agent, act_agent and apply_effect write it; the host drains effects into Apply and events into Events</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6387,7 +6641,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Core Agent state (needs, fear, health, memory, state)</t>
+          <t>Core Agent state (needs, fear, health, memory, state) and its Outbox (TYP-24)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -6477,7 +6731,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="29" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CMP-06</t>
@@ -6485,7 +6739,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>NavAgent</t>
+          <t>MoveIntent / MoveFailed</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -6495,95 +6749,95 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>current path, target</t>
+          <t>MoveIntent: target, gait, speed, gaze · MoveFailed: marker, target unreachable</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>act_system</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+          <t>act_system / Game</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CMP-07</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ScentMark</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>species, kind, meaning, age</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>apply_effects_system</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>6.2 Components (editor)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>On entity</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Data / meaning</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Written by</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CMP-11</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Tooltip</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Any control</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>title, what, effect (i18n keys)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Builders</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="29" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>CMP-12</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>UiItem</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Any control</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>item_id: &amp;'static str (e.g. "SCR-02-17") — links runtime UI to the External Design for tests</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -6595,181 +6849,181 @@
     <row r="17" ht="29" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>CMP-12</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>UiItem</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Any control</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>item_id: &amp;'static str (e.g. "SCR-02-17") — links runtime UI to the External Design for tests</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Builders</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>CMP-13</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>GraphNode / GraphEdge / Port</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Graph UI</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>node id, kind; edge id; port side</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>render_graph</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CMP-14</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>LiveMark</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Graph node</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>live highlight and score</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>live_highlight_system</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="29" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="29" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CMP-15</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>DialogRoot / MenuRoot / ToastRoot</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Overlays</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>shell</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CMP-16</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>AreaView(Area)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Main view root</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Despawned on area exit</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>shell::nav</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>6.3 Resources</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Crate</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>RES-01</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>NoeticConfig</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>noetic</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>think_hz (10), fixed_dt, max_agents, debug flags</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Inserted by plugin</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>RES-02</t>
+          <t>RES-01</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>WorldViewCache</t>
+          <t>NoeticConfig</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -6779,74 +7033,74 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Spatial grid of props and agents (cell 8 m)</t>
+          <t>think_hz (10), fixed_dt, secs_per_game_hour, max_agents, debug flags</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>sync_world_system</t>
+          <t>Inserted by plugin</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>RES-03</t>
+          <t>RES-02</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ExtRegistry</t>
+          <t>WorldViewCache</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>core/noetic</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Registered custom actions, conditions, sensors, curves</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
+          <t>Spatial grid of props and agents (cell 8 m)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>sync_world_system</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>RES-04</t>
+          <t>RES-03</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>ExtRegistry</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>core/noetic</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>TYP-21</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Autosaved</t>
-        </is>
-      </c>
+          <t>Registered custom actions, conditions, sensors, curves</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>RES-05</t>
+          <t>RES-04</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Project</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -6856,24 +7110,24 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Undo/redo stacks of Box&lt;dyn Command&gt;</t>
+          <t>TYP-21</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Max 200</t>
+          <t>Autosaved</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>RES-06</t>
+          <t>RES-05</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>SimHost</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -6883,20 +7137,24 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>SimWorld, running, speed, tick accumulator</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr"/>
+          <t>Undo/redo stacks of Box&lt;dyn Command&gt;</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Max 200</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>RES-07</t>
+          <t>RES-06</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Selection</t>
+          <t>SimHost</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -6906,7 +7164,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>None | Species | Activity | Node | Agent | Terrain</t>
+          <t>SimWorld, running, speed, tick accumulator</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -6914,85 +7172,85 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>RES-07</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>None | Species | Activity | Node | Agent | Terrain</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>RES-08</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>ShellLayout</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>left_open, right_open, widths</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="29" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="29" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>RES-09</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>GraphView / WorldCam / Layers / WorldTool</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>View state per area</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Saved in project ui_state</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>RES-10</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>RemoteClient</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>editor</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>state, addr, last data, task</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>RES-11</t>
+          <t>RES-10</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>I18n</t>
+          <t>RemoteClient</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -7002,496 +7260,492 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Language table for labels and messages (English default)</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>state, addr, last data, task</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>RES-11</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>I18n</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Language table for labels and messages (English default)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>RES-12</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>UiTheme</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>bevy_feathers</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>create_dark_theme() — default, not modified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>DP-05</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="37" ht="29" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>RES-13</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>AgentOrder</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>noetic</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(AgentId, Entity) sorted by id; next id counter</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>sync_world_system; Think, Act and Apply walk it (PF-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="29" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>RES-14</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>NoeticClock</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>noetic</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>hour, light, fixed step counter</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Advanced by the plugin each fixed step; the game may set the hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>6.4 Events / messages</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Crate</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Payload</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Consumers</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>EVT-01</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>NoeticAnimEvent</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>noetic</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>entity, event: String, clip: Option&lt;String&gt;, looping</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Game animation</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>EVT-02</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>NoeticAlarm</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>noetic</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>entity, kind</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Game audio</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>EVT-03</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>NoeticDied</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>noetic</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Game</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>EVT-04</t>
+          <t>EVT-01</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>EditorCommand</t>
+          <t>NoeticAnimEvent</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Box&lt;dyn Command&gt; to apply</t>
+          <t>entity, event: String, clip: Option&lt;String&gt;, looping</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>history system</t>
+          <t>Game animation</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>EVT-05</t>
+          <t>EVT-02</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ToastRequest</t>
+          <t>NoeticAlarm</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>MsgId, args, undo token</t>
+          <t>entity, kind</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>shell::toast</t>
+          <t>Game audio</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>EVT-03</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>NoeticDied</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>noetic</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>EVT-04</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>EditorCommand</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Box&lt;dyn Command&gt; to apply</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>history system</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>EVT-05</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>ToastRequest</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>MsgId, args, undo token</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>shell::toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>EVT-06</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>ProjectChanged</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>what changed (species id, activity id…)</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>compile, autosave, views</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>6.5 States</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Crate</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Values</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>STA-01</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Brain | World | Species | Individuals</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>OnEnter/OnExit spawn views</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="29" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="52" ht="29" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>STA-02</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>WorldMode (SubState of Area::World)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Simulate | EditTerrain</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>STA-03</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>RemoteState</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Disconnected | Connecting | Connected</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>6.6 Schedules and system sets (order inside a frame)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Schedule / set</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Crate</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Systems (API)</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>Run condition</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>SYS-01</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>PreUpdate</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>shortcut_system (API-APP-009), pointer/drag input (API-BRN-025)</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>always</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="29" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>SYS-02</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>FixedUpdate · NoeticSet::Sync</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>noetic</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>sync_world_system (API-RT-004)</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>agents exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="29" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>SYS-03</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>FixedUpdate · NoeticSet::Think</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>noetic</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>think_system (API-RT-005): needs, perceive, memory, fear, threat, choose</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>every 1/think_hz per agent (round robin)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="29" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>SYS-04</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>FixedUpdate · NoeticSet::Act</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>noetic</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>run_step, locomotion, fights, marks</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>every fixed step</t>
         </is>
       </c>
     </row>
     <row r="58" ht="29" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>SYS-05</t>
+          <t>SYS-02</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>FixedUpdate · NoeticSet::Events</t>
+          <t>FixedUpdate · NoeticSet::Sync</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7501,145 +7755,253 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>anim_event_system (API-RT-006)</t>
+          <t>sync_world_system (API-RT-004)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>events pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
+          <t>agents exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="29" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>SYS-06</t>
+          <t>SYS-03</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>FixedUpdate (editor)</t>
+          <t>FixedUpdate · NoeticSet::Think</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>sim_host_system (API-SIM-007) — calls core::sim::tick</t>
+          <t>think_system (API-RT-005): needs, perceive, memory, fear, threat, choose</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>SimHost.running</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
+          <t>agents with think_due (API-COR-023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="29" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>SYS-07</t>
+          <t>SYS-04</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Update · EditorSet::Apply</t>
+          <t>FixedUpdate · NoeticSet::Act</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>apply EditorCommand, compile on ProjectChanged</t>
+          <t>act_system (API-RT-010): run_step, movement intent, fights, marks</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>events pending</t>
+          <t>every fixed step</t>
         </is>
       </c>
     </row>
     <row r="61" ht="29" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>SYS-08</t>
+          <t>SYS-11</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Update · EditorSet::Views</t>
+          <t>FixedUpdate · NoeticSet::Apply</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>render_graph, live_highlight, render_world, render_day_strip, agent_debug_view, status_bar</t>
+          <t>apply_effects_system (API-RT-011)</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>per area (in_state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
+          <t>every fixed step, after Act</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="29" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>SYS-09</t>
+          <t>SYS-05</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Update · EditorSet::Overlay</t>
+          <t>FixedUpdate · NoeticSet::Events</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>noetic</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>tooltip_system, toast timer, remote_poll_system</t>
+          <t>anim_event_system (API-RT-006)</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>events pending</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
+          <t>SYS-06</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>FixedUpdate (editor)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>sim_host_system (API-SIM-007) — calls core::sim::tick</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>SimHost.running</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>SYS-07</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Update · EditorSet::Apply</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>apply EditorCommand, compile on ProjectChanged</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>events pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="29" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>SYS-08</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Update · EditorSet::Views</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>render_graph, live_highlight, render_world, render_day_strip, agent_debug_view, status_bar</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>per area (in_state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>SYS-09</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Update · EditorSet::Overlay</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>tooltip_system, toast timer, remote_poll_system</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
           <t>SYS-10</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Last</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>editor</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>autosave_system (API-PRJ-012)</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Project changed</t>
         </is>

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -256,7 +256,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9515475" cy="4138746"/>
+    <ext cx="9515475" cy="3628989"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="4105275"/>
+    <ext cx="8086773" cy="4105275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t xml:space="preserve">0.11</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1118,115 +1118,141 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reacting</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reacting</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no next &amp; fear &gt; threshold</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repeat the last reaction (e.g. hide)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
           <t>Reacting</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Choosing</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>no next &amp; fear &lt; threshold</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no next &amp; fear ≤ threshold</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>end reaction</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>API-COR-006</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="29" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Choosing / InActivity</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Fighting</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>urge to fight ≥ 70 &amp; rival ≤ 12 m, or challenged (Effect::Challenge) and fighting back</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>approach rival / answer the challenge</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>API-COR-013, API-COR-022</t>
         </is>
       </c>
     </row>
     <row r="53" ht="29" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>Choosing / InActivity</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>Fighting</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>urge to fight ≥ 70 &amp; rival ≤ 12 m, or challenged (Effect::Challenge) and fighting back</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>approach rival / answer the challenge</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-COR-013 in the rival's act; API-COR-022 only records the challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="29" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Fighting</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Reacting / Choosing</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>loses or flees / wins or cooldown</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>API-COR-013</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Alive</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Dead</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>health = 0</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">health ≤ 0</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>emit Died; stop processing</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>API-COR-014</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>7.2 Editor states (STA-01…03)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1"/>
     <row r="58" ht="15" customHeight="1"/>
     <row r="59" ht="15" customHeight="1"/>
     <row r="60" ht="15" customHeight="1"/>
@@ -1250,6 +1276,7 @@
     <row r="78" ht="15" customHeight="1"/>
     <row r="79" ht="15" customHeight="1"/>
     <row r="80" ht="15" customHeight="1"/>
+    <row r="81" ht="15" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId1"/>
@@ -1457,7 +1484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1520,7 +1547,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Functions return Result&lt;T, NoeticError&gt;; indexing via get(); clippy::unwrap_used = deny in core.</t>
+          <t xml:space="preserve">Functions return Result with the area's error type (9.2), wrapped in NoeticError (TYP-22) at the crate boundary; indexing via get(); clippy::unwrap_used = deny in core.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1714,7 +1741,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>API-PRJ-002, API-SPC-002/006</t>
+          <t xml:space="preserve">API-PRJ-002, API-SPC-002/006, API-BRN-013, API-IND-009</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1824,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>wrap std::io::Error, ParseError</t>
+          <t xml:space="preserve">wrap std::io::Error, ImportError (parse, migrate)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1806,118 +1833,250 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>9.3 Logging (tracing via bevy_log)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Content</t>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERR-09</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CompileError</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-BRN-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERR-10</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FieldError</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Range{field, min, max} (the value is clamped)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-SPC-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERR-11</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExportError</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serialize(msg)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-IO-001</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>LOG-01</t>
+          <t xml:space="preserve">ERR-12</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>noetic::sim</t>
+          <t xml:space="preserve">ImportError</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>trace</t>
+          <t xml:space="preserve">Parse(ERR-01) | Validate(ERR-02) | Migrate(ERR-03)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Per-agent decisions (only with NOETIC_TRACE=1)</t>
+          <t xml:space="preserve">API-IO-002, API-IO-005</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>LOG-02</t>
+          <t xml:space="preserve">ERR-13</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>noetic::asset</t>
+          <t xml:space="preserve">ClipError</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>info / warn / error</t>
+          <t xml:space="preserve">Unavailable</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Load, reload, validation warnings, errors</t>
+          <t xml:space="preserve">API-IO-006</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">ERR-14</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExtError</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duplicate(id)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API-RT-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>9.3 Logging (tracing via bevy_log)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>LOG-01</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">noetic::think</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>trace</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Per-agent decisions (only with NOETIC_TRACE=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>LOG-02</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>noetic::asset</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>info / warn / error</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Load, reload, validation warnings, errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>LOG-03</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>noetic::debug</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Remote connections</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>LOG-04</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>noetic_editor</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>info / error</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Project save/load, command errors</t>
         </is>
@@ -2125,7 +2284,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Bevy queries have no stable order. sync_world_system gives each new agent an AgentId from a counter (new agents of the same step sorted by Entity); AgentOrder keeps (AgentId, Entity) sorted, and Think, Act and Apply walk it. The editor SimWorld keeps its agents in id order.</t>
+          <t xml:space="preserve">Bevy queries have no stable order. sync_world_system gives each new agent an AgentId from a counter (new agents of the same step sorted by Entity); AgentOrder keeps (AgentId, Entity) sorted, and Act and Apply walk it; Think may run in parallel (PF-04) because each agent writes only itself. The editor SimWorld keeps its agents in id order.</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2549,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Every API with logic (core, rules, compile, rebalance). Cases in Detailed Design › Unit Tests.</t>
+          <t xml:space="preserve">The core logic APIs listed in Detailed Design › Unit Tests; logic APIs without their own cases yet are covered by the golden determinism test (TST-03) until they get them.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -2569,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2763,6 +2922,94 @@
       <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Coherence review: new TYP-24 Outbox carries an agent's effects and SimEvents; WorldView gets hour() and marks_near(); CMP-02 holds the Outbox; a challenged agent fights back or flees (7.1); MOD-062…064 for model, events and tuning; MOD-015 and MOD-028 API counts; SEQ-01 covers PRC-17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>heryk</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Individuals are saved: TYP-21 Project gets individuals: Vec&lt;SavedAgent&gt;, copied from the SimWorld on save and respawned on load; EVT-06 also names the agent that was spawned or edited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review against the other documents: TYP-01 carries schema_version and is written as NoeticSpecies; TYP-08 Activity has no name (it is the map key); TYP-11 health: f32 and limping; TYP-17 next_u64; TYP-21 settings; CMP-02 lists every system that touches the Outbox; SYS-03/04 list the stages of COR-020/021; AgentOrder belongs to MOD-027 only; MOD-029 gets API-BRN-026; the 7.1 guards match ALG-06 and ALG-11 (≤); new ERR-09…14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each document checked against itself: the editor depends on plain noetic (the debug feature is for games); SimHost moves to noetic_editor::sim_host (MOD-057), shared by the areas, and DEP-05 lists inspector; DEP-03/04 allow bevy next to noetic; NoeticError wraps the area errors (TYP-22, EP-01); sync_world_system advances NoeticClock (SYS-02, RES-14); act_system writes MoveIntent through noetic::nav and reads MoveFailed (CMP-06); ExtRegistry is a core type with a noetic Resource (RES-03); LOG-01 logs from noetic::think; TYP-21 lives in project::tree and uses locked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="68" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.11</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The folder layout lists sim_host.rs; the editor lists slotmap; TYP-10 names every enum; TYP-11 keeps the fight, mark and score state; WorldView gives secs_per_game_hour and forget; NoeticAgent requires AgentBrainState and MoveIntent; WorldViewCache holds scent marks and apply_effects_system ages them; the clock advances every fixed step (SYS-02); SYS-03/04 name alarms and the reaction countdown; SYS-12 Startup and SYS-13 hot reload; 7.1 repeats the last reaction and lets the rival answer in its act; ImportError covers parse and migrate, LoadError wraps it; Think may run in parallel (PF-09); TST-01 says which APIs have cases.</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3161,7 +3408,7 @@
     <row r="5" ht="216.5" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>noetic/
+          <t xml:space="preserve">noetic/
 ├─ Cargo.toml                 # [workspace] members, shared deps, bevy pinned
 ├─ crates/
 │  ├─ noetic_core/            # no Bevy dependency
@@ -3172,7 +3419,7 @@
 │  │  └─ src/{lib.rs, plugin.rs, asset.rs, sync.rs, think.rs, anim.rs, nav.rs, debug.rs}
 │  └─ noetic_editor/          # binary
 │     └─ src/{main.rs, app.rs, theme.rs, i18n.rs, shell/, project/, brain/, world/,
-│             inspector.rs, species/, individuals/, io/, remote.rs}
+│             inspector.rs, sim_host.rs, species/, individuals/, io/, remote.rs}
 ├─ assets/                    # built-in species *.noetic.ron, i18n tables, logo
 ├─ examples/                  # rabbit_in_game, custom_action, remote_debug
 ├─ tests/                     # workspace integration + golden files
@@ -3272,7 +3519,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>bevy (ui, feathers, winit, render), noetic[debug], arboard, rfd, ureq (BRP client)</t>
+          <t xml:space="preserve">bevy (ui, feathers, winit, render), noetic, arboard, rfd, ureq (BRP client), slotmap</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4303,7 +4550,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Think, act and apply systems; NoeticAgent, AgentBrainState, AgentOrder.</t>
+          <t xml:space="preserve">Think, act and apply systems; NoeticAgent, AgentBrainState.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -4338,11 +4585,11 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>API-BRN-013, API-BRN-017, API-BRN-024</t>
+          <t xml:space="preserve">API-BRN-013, API-BRN-017, API-BRN-024, API-BRN-026</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
@@ -5163,7 +5410,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::world::host</t>
+          <t xml:space="preserve">noetic_editor::sim_host</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -5173,7 +5420,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Simulation host in the editor.</t>
+          <t xml:space="preserve">Simulation host in the editor, shared by the brain, world, individuals and inspector areas.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -5502,7 +5749,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Games depend on noetic only.</t>
+          <t xml:space="preserve">Games depend on noetic (and bevy), never on noetic_core directly.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -5519,7 +5766,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor depends on noetic only, never on internal paths.</t>
+          <t xml:space="preserve">Of the workspace crates, noetic_editor depends on noetic only (it also uses bevy), never on internal paths.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5536,7 +5783,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Inside the editor: shell ← (brain, world, species, individuals, io, remote) ← project. Feature modules never import each other; they communicate through Commands/Events and shared Resources (Project, Selection, SimHost).</t>
+          <t xml:space="preserve">Inside the editor: shell ← (brain, world, species, individuals, inspector, io, remote) ← project. Feature modules never import each other; they communicate through Commands/Events and shared Resources (Project, Selection, and SimHost in noetic_editor::sim_host).</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -5803,12 +6050,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>species, color, locomotion, group, shelter, routine, senses, needs, health, personality, quirks, scent_marks, brain, activities, animation_clips</t>
+          <t xml:space="preserve">schema_version, species, color, locomotion, group, shelter, routine, senses, needs, health, personality, quirks, scent_marks, brain, activities, animation_clips</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Serialize, Deserialize, Clone, Debug, Asset (via newtype in bevy)</t>
+          <t xml:space="preserve">Serialize, Deserialize, Clone, Debug; RON name NoeticSpecies (FMT-01); the noetic crate wraps it in the NoeticSpecies asset</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6258,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>name, need: Need, curve: Curve, weight: f32, steps: Vec&lt;Step&gt;</t>
+          <t xml:space="preserve">need: Need, curve: Curve, weight: f32, steps: Vec&lt;Step&gt;; its name is its key in the activity map</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -6052,7 +6299,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Need / Curve / StepKind / Routine / GroupKind / Shelter / Trait</t>
+          <t xml:space="preserve">Need / Curve / StepKind / Routine / GroupKind / Shelter / Trait / LocomotionKind / MarkKind / Meaning / AlarmKind / FleeTarget</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -6099,7 +6346,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>id, species, name, seed, traits: TraitMap, quirks, locked, needs: Needs, fear, health: Health, memory: Memory, state: AgentState, pos, heading, rng: Rng</t>
+          <t xml:space="preserve">id, species, name, seed, traits: TraitMap, quirks, locked, needs: Needs, fear, health: f32, limping: bool, memory: Memory, state: AgentState, pos, heading, rng: Rng, fight_urge, fight_cooldown, last_mark, last_scores</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -6195,7 +6442,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>fn nearest(kind, pos, r) / fn neighbours(pos, r) / fn terrain_at(pos) / fn light() / fn wind() / fn hour() / fn marks_near(pos, r)</t>
+          <t xml:space="preserve">fn nearest(kind, pos, r) / fn neighbours(pos, r) / fn terrain_at(pos) / fn light() / fn wind() / fn hour() / fn marks_near(pos, r) / fn secs_per_game_hour() / fn forget()</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -6283,7 +6530,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Pcg32 wrapper; next_u32, unit, range, below</t>
+          <t xml:space="preserve">Pcg32 wrapper; seed, next_u32, next_u64, unit, range, below</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -6388,7 +6635,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="29" customHeight="1">
+    <row r="38" ht="42" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>TYP-21</t>
@@ -6406,17 +6653,17 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>noetic_editor::project</t>
+          <t xml:space="preserve">noetic_editor::project::tree</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>folders, species, activities, presets, world_layout, ui_state, path</t>
+          <t xml:space="preserve">folders, species, activities, presets, world_layout (ENT-09 World), individuals: Vec&lt;SavedAgent { species, name, seed, position, traits, quirks, locked }&gt;, settings, ui_state, path</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Serialize (FMT-02)</t>
+          <t>Serialize (FMT-02); individuals copied from the SimWorld on save, respawned on load</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6685,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>noetic_core</t>
+          <t xml:space="preserve">noetic_core (lib.rs)</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Parse | Validate | Migrate | Io (thiserror)</t>
+          <t xml:space="preserve">Parse | Validate | Migrate | Export | Ext | Io (thiserror); wraps ERR-01…03, ERR-11 and ERR-14 at the crate boundary</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -6533,7 +6780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6614,7 +6861,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>species: Handle&lt;NoeticSpecies&gt;, seed: Option&lt;u64&gt;, name: Option&lt;String&gt;; required: Transform</t>
+          <t xml:space="preserve">species: Handle&lt;NoeticSpecies&gt;, seed: Option&lt;u64&gt;, name: Option&lt;String&gt;; required: Transform, AgentBrainState, MoveIntent (Bevy required components)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -6646,7 +6893,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>think_system</t>
+          <t xml:space="preserve">think_system, act_system; anim_event_system and apply_effects_system drain its Outbox</t>
         </is>
       </c>
     </row>
@@ -6754,7 +7001,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>act_system / Game</t>
+          <t xml:space="preserve">act_system writes MoveIntent through noetic::nav (API-RT-008); the game writes MoveFailed, which act_system reads (the step fails)</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7307,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Spatial grid of props and agents (cell 8 m)</t>
+          <t xml:space="preserve">Spatial grid of props, agents and scent marks (cell 8 m)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -7082,7 +7329,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>core/noetic</t>
+          <t xml:space="preserve">noetic_core (type) / noetic (Resource)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -7369,7 +7616,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Advanced by the plugin each fixed step; the game may set the hour</t>
+          <t xml:space="preserve">Advanced by sync_world_system (API-RT-004, PRC-01) at the start of each fixed step; the game may set the hour</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7807,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>what changed (species id, activity id…)</t>
+          <t>what changed (species id, activity id, agent spawned or edited…)</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -7755,12 +8002,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>sync_world_system (API-RT-004)</t>
+          <t xml:space="preserve">sync_world_system (API-RT-004): advances NoeticClock, then syncs the world</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>agents exist</t>
+          <t xml:space="preserve">every fixed step</t>
         </is>
       </c>
     </row>
@@ -7782,7 +8029,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>think_system (API-RT-005): needs, perceive, memory, fear, threat, choose</t>
+          <t xml:space="preserve">think_system (API-RT-005): heal, needs, perceive, memory, fear, threat (queues alarms, PRC-09), choose (API-COR-020)</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -7809,7 +8056,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>act_system (API-RT-010): run_step, movement intent, fights, marks</t>
+          <t xml:space="preserve">act_system (API-RT-010): counts down a reaction, or runs run_step, follow_group, fight, leave_mark, locomotion (API-COR-021)</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -7836,7 +8083,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>apply_effects_system (API-RT-011)</t>
+          <t xml:space="preserve">apply_effects_system (API-RT-011): applies effects, then ages scent marks (API-COR-015)</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -7890,7 +8137,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>sim_host_system (API-SIM-007) — calls core::sim::tick</t>
+          <t xml:space="preserve">sim_host_system (API-SIM-007) — calls noetic::sim::tick (core, re-exported)</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -8004,6 +8251,60 @@
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Project changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-12</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Startup</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">editor</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spawn_shell (API-APP-008)</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">once</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-13</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Update</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">noetic</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hot_reload_system (API-RT-003)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on AssetEvent&lt;NoeticSpecies&gt;</t>
         </is>
       </c>
     </row>

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.11</t>
+          <t xml:space="preserve">0.12</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3010,6 +3010,28 @@
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">The folder layout lists sim_host.rs; the editor lists slotmap; TYP-10 names every enum; TYP-11 keeps the fight, mark and score state; WorldView gives secs_per_game_hour and forget; NoeticAgent requires AgentBrainState and MoveIntent; WorldViewCache holds scent marks and apply_effects_system ages them; the clock advances every fixed step (SYS-02); SYS-03/04 name alarms and the reaction countdown; SYS-12 Startup and SYS-13 hot reload; 7.1 repeats the last reaction and lets the rival answer in its act; ImportError covers parse and migrate, LoadError wraps it; Think may run in parallel (PF-09); TST-01 says which APIs have cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="68" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 Workspace lists rand instead of rand_core for noetic_core, with default features off (no thread_rng) and alloc for choose_weighted.</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3493,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>serde, ron, rand_core + rand_pcg, thiserror, glam (math), smallvec</t>
+          <t>serde, ron, rand + rand_pcg, thiserror, glam (math), smallvec</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.12</t>
+          <t xml:space="preserve">0.13</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3032,6 +3032,28 @@
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2 Workspace lists rand instead of rand_core for noetic_core, with default features off (no thread_rng) and alloc for choose_weighted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="68" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.13</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 Workspace lists enum-map for noetic_core: Needs is an EnumMap&lt;Need, f32&gt; (TYP-11).</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3515,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>serde, ron, rand + rand_pcg, thiserror, glam (math), smallvec</t>
+          <t>serde, ron, rand + rand_pcg, thiserror, glam (math), smallvec, enum-map (one value per enum variant)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.13</t>
+          <t xml:space="preserve">0.14</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3054,6 +3054,28 @@
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2 Workspace lists enum-map for noetic_core: Needs is an EnumMap&lt;Need, f32&gt; (TYP-11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="68" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.14</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TYP-10 names GoToTarget, the target of StepKind::GoTo.</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6365,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Need / Curve / StepKind / Routine / GroupKind / Shelter / Trait / LocomotionKind / MarkKind / Meaning / AlarmKind / FleeTarget</t>
+          <t xml:space="preserve">Need / Curve / StepKind / GoToTarget / Routine / GroupKind / Shelter / Trait / LocomotionKind / MarkKind / Meaning / AlarmKind / FleeTarget</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">

--- a/docs/04_internal_design.xlsx
+++ b/docs/04_internal_design.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.14</t>
+          <t xml:space="preserve">0.15</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Rust stable, edition 2024, rustfmt default, clippy -D warnings (pedantic for core).</t>
+          <t xml:space="preserve">Rust stable, edition 2024, rustfmt default, clippy -D warnings with the extra lints picked one by one in the workspace [lints]; no clippy::pedantic as a whole.</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>#![forbid(unsafe_code)] in all crates.</t>
+          <t xml:space="preserve">unsafe_code = "forbid" in the workspace [lints], which every crate inherits: the same as #![forbid(unsafe_code)] in each.</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Every pub item has a doc comment with the API ID, e.g. /// API-COR-007 weighted_pick.</t>
+          <t xml:space="preserve">Every pub item that implements a design ID starts its doc comment with that ID, e.g. /// API-COR-007 Picks one item…; helpers that implement none stay pub(crate).</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>1000 ticks of the default world with seed 42 → hash of agent states equals stored hash.</t>
+          <t xml:space="preserve">1000 ticks of the default world (four rabbits, built in the test) with seed 42 → FNV-1a hash of the world's Debug text equals the GOLDEN constant.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>tests/golden/*.ron</t>
+          <t xml:space="preserve">tests/golden.rs</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3076,6 +3076,28 @@
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TYP-10 names GoToTarget, the target of StepKind::GoTo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heryk</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review of M1: MOD-064 noetic_core::tuning is dropped, every tuning constant is named in the Config section of the file that uses it; TYP-14 is implemented by world::Clock so far and SimWorld never lends itself as a whole, since tick holds its agents mutably: the rest of the world is the view, with positions from the grid built before Think; TST-03 keeps the golden hash as a constant in tests/golden.rs, FNV-1a over the world's Debug text; CS-01 drops clippy::pedantic, since the lints worth having are picked one by one in the workspace [lints]; CS-02 is the workspace lint; CS-04 follows CONTRIBUTING (the design ID starts the doc of the pub items that implement one); the dependency rules are checked by review until the CI exists.</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3502,7 @@
 │  ├─ noetic_core/            # no Bevy dependency
 │  │  └─ src/{lib.rs, model/, agent/, world/, sim.rs, perception.rs, emotion.rs, reaction.rs,
 │  │          utility.rs, steps.rs, social.rs, conflict.rs, territory.rs, locomotion.rs,
-│  │          personality.rs, rng.rs, io/, ext.rs, sandbox.rs, tuning.rs, events.rs}
+│  │          personality.rs, rng.rs, io/, ext.rs, sandbox.rs, events.rs}
 │  ├─ noetic/                 # the crate games add: Bevy plugin, pub use noetic_core, prelude
 │  │  └─ src/{lib.rs, plugin.rs, asset.rs, sync.rs, think.rs, anim.rs, nav.rs, debug.rs}
 │  └─ noetic_editor/          # binary
@@ -5696,7 +5718,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Initial tuning constants of the ALG-xx formulas, in one place.</t>
+          <t xml:space="preserve">Dropped (0.15): every tuning constant is named in the Config section of the file that uses it (CONTRIBUTING).</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -5752,7 +5774,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Enforced in CI (cargo-deny + a test that greps Cargo metadata)</t>
+          <t xml:space="preserve">To be enforced in CI (cargo-deny + a test that greps Cargo metadata); until the CI exists, review checks them.</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6503,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Editor owns one; games use WorldViewCache instead</t>
+          <t xml:space="preserve">Editor owns one; every field but agents and species makes up its WorldView (TYP-14); games use WorldViewCache instead</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6535,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Read-only. Implemented by SimWorld and by noetic::sync::WorldViewCache; per-agent core functions get &amp;dyn WorldView, never the world itself</t>
+          <t xml:space="preserve">Read-only. Implemented by world::Clock while the view asks only hour() and secs_per_game_hour() (M1); SimWorld and noetic::sync::WorldViewCache implement it once it asks more, but never SimWorld as a whole: tick holds its agents mutably, so the view is the rest of the world (the clock now; wind, terrain, marks, stimuli and the grid of positions built before Think later) in a field of its own. Per-agent core functions get &amp;dyn WorldView, never the world itself</t>
         </is>
       </c>
     </row>
